--- a/emergency_report_forms/034_disaster_recovery_check_in_form--emergency_report_forms.xlsx
+++ b/emergency_report_forms/034_disaster_recovery_check_in_form--emergency_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -693,12 +693,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>emergency_contact_number</t>
+          <t>emergency_contact_number_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Emergency Contact Number</t>
+          <t>Emergency Contact Number 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -940,7 +940,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shelter Name</t>
+          <t>Shelter Name (2)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -958,12 +958,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>shelter_name</t>
+          <t>shelter_name_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shelter Name</t>
+          <t>Shelter Name (3)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>shelter_address</t>
+          <t>shelter_address_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shelter Address</t>
+          <t>Shelter Address 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>shelter_contact_number</t>
+          <t>shelter_contact_number_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shelter Contact Number</t>
+          <t>Shelter Contact Number 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>shelter_contact_number</t>
+          <t>shelter_contact_number_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Shelter Contact Number</t>
+          <t>Shelter Contact Number 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>shelter_contact_method</t>
+          <t>shelter_contact_method_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shelter Contact Method</t>
+          <t>Shelter Contact Method 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
